--- a/MyVetHelp_Resource_Database.xlsx
+++ b/MyVetHelp_Resource_Database.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -668,6 +667,11 @@
           <t>No form — call or text</t>
         </is>
       </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>1) Call 988 and press 1, or text 838255, any time day or night. 2) A trained responder (many are veterans themselves) talks through the crisis with you immediately. 3) If needed, they can connect you to local VA emergency services or follow-up care -- no enrollment or paperwork required at any point.</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>https://www.veteranscrisisline.net/</t>
@@ -715,6 +719,11 @@
           <t>No form — walk-in or call</t>
         </is>
       </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>1) Call or walk in to the Savannah Vet Center directly -- no referral needed. 2) An intake counselor talks with you briefly to understand what kind of support fits (individual, group, or family counseling). 3) Sessions are scheduled directly with a counselor, often starting within days, not months.</t>
+        </is>
+      </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>https://www.va.gov/find-locations/</t>
@@ -762,6 +771,11 @@
           <t>No form — schedule after health care enrollment (see VA Form 10-10EZ below)</t>
         </is>
       </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>1) Enroll in VA health care first using Form 10-10EZ (see the VA Health Care Enrollment entry in this list for that process). 2) Once enrolled, call the Savannah clinic directly to schedule your first primary care appointment. 3) At your visit, staff can refer you to specialty or mental health services at the same location as needed.</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>https://www.va.gov/charleston-health-care/locations/savannah-va-clinic/</t>
@@ -861,6 +875,11 @@
           <t>No form — website intake</t>
         </is>
       </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>1) Visit mvpsavannah.org and fill out the contact/intake form describing what you need help with. 2) A caseworker follows up, usually within a few business days, to discuss options. 3) They connect you directly with financial aid, VA benefits help, or other local resources based on your situation.</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>https://mvpsavannah.org/</t>
@@ -908,6 +927,11 @@
           <t>No public form — VA homeless program referral</t>
         </is>
       </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>1) Contact a VA Social Worker or Homeless Veteran Coordinator through your local VA medical center, or call the National Call Center for Homeless Veterans. 2) They assess your situation and eligibility. 3) If eligible, VA case management staff coordinate directly with the local public housing authority to issue a housing voucher alongside ongoing case support.</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
           <t>https://www.va.gov/homeless/hud-vash.asp</t>
@@ -955,6 +979,11 @@
           <t>VA Form 28-1900</t>
         </is>
       </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>1) Apply online at va.gov/careers-employment/vocational-rehabilitation using VA Form 28-1900, or apply in person at a VA regional office. 2) Attend an orientation and evaluation to determine your employment barrier and entitlement. 3) Work with a Vocational Rehabilitation Counselor to build an individualized plan (training, education, or direct job placement). 4) VA covers approved costs while you complete the plan.</t>
+        </is>
+      </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
           <t>https://www.va.gov/careers-employment/vocational-rehabilitation/</t>
@@ -1002,6 +1031,11 @@
           <t>No form — Employ Georgia registration</t>
         </is>
       </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>1) Visit or call the Savannah Career Center and let them know you're a veteran -- this gives you priority of service by law. 2) Register with Employ Georgia (their online job system) if you haven't already. 3) A staff member works with you on job search, resume help, and referrals to openings prioritized for veterans.</t>
+        </is>
+      </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
           <t>https://dol.georgia.gov/veterans-employment-services</t>
@@ -1101,6 +1135,11 @@
           <t>No federal form — MyGeorgiaSouthern Benefits Request Form</t>
         </is>
       </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>1) Log in to the MyGeorgiaSouthern student portal. 2) Submit a Benefits Request form under the Military and Veterans Services section. 3) Upload your Certificate of Eligibility if using GI Bill benefits. 4) The office certifies your enrollment each term directly with the VA -- you only need to notify them again if your schedule changes.</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
           <t>https://www.georgiasouthern.edu/admissions-aid/military-and-veterans</t>
@@ -1148,6 +1187,11 @@
           <t>VA Form 28-1900</t>
         </is>
       </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>1) Apply online at va.gov/careers-employment/vocational-rehabilitation using VA Form 28-1900. 2) Attend an evaluation with a Vocational Rehabilitation Counselor. 3) If an education path is approved as part of your plan, VA covers tuition and provides support services while you complete your program.</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
           <t>https://www.va.gov/careers-employment/vocational-rehabilitation/</t>
@@ -1265,6 +1309,110 @@
       <c r="J18" s="4" t="inlineStr">
         <is>
           <t>National</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Chatham County VSO Office (local)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Disability Benefits</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Local Veterans Service Officers who help file and track VA disability claims in person, located inside the Savannah VA Outpatient Clinic.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Any Chatham County veteran or dependent; English and Spanish assistance available</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Call or walk in to schedule a free appointment -- no cost, no obligation.</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>VA Form 21-22</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>1) Call ahead to schedule (walk-ins also accepted). 2) Bring your DD-214 and any medical records related to your claim. 3) The VSO completes and files your claim paperwork with you and can track its status going forward.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>https://veterans.georgia.gov/locations/savannah</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>(912) 920-0214</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Local — Savannah, GA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>DAV (Disabled American Veterans) — Claims Assistance</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Disability Benefits</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>National nonprofit providing free, expert help filing and appealing VA disability claims, with local chapters in the Savannah area.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Any veteran -- membership is not required to get claims help</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Call the national line to be connected to your nearest office, or contact a local Savannah chapter directly.</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>No form — DAV staff complete VA Form 21-526EZ with you</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>1) Call 1-877-426-2838 (or a local Savannah chapter) to request help. 2) A DAV National Service Officer reviews your situation and gathers supporting evidence with you. 3) They file the claim on your behalf and represent you through any appeals, entirely free.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dav.org/find-your-local-office/</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>1-877-426-2838 (national); Savannah Chapter 8: (912) 800-3344</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Local — Savannah, GA / National</t>
         </is>
       </c>
     </row>
